--- a/AAII_Financials/Quarterly/SKFRY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SKFRY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="92">
   <si>
     <t>SKFRY</t>
   </si>
@@ -656,177 +656,181 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -869,86 +873,89 @@
       <c r="P8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="3">
         <v>2484100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2410300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2288600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2166200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1916900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1909400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1932300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1878400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1848800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1833000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1704900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2217000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2411300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2547600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2598300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2505700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2432600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2243400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2350900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2136800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2096900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2005000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2177400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2225100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2126500</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2027700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,86 +998,89 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3">
         <v>1862200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1855200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1719900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1553500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1398400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1382100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1345800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1335600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1158400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1410700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1391400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1680600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1864800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1934000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1945800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1867300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1892900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1695800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1755900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1591400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1581300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1514100</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1628500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1660500</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1627500</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1518100</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1113,86 +1123,89 @@
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3">
         <v>621900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>555100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>568700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>612700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>518400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>527400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>586500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>542900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>690400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>422300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>313500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>536300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>546600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>613600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>652500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>638400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>539700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>547600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>595000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>545400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>515600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>490900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>549000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>564600</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>498900</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>509600</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1279,33 +1293,33 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3">
         <v>81000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>75200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>78000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>72200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>70100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>61400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>63600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>61700</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,8 +1496,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1523,8 +1543,8 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1601,8 +1621,11 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1645,8 +1668,8 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,8 +1790,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1808,86 +1835,89 @@
       <c r="P17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="3">
         <v>2281500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2224200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2135700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1887400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1680000</v>
-      </c>
-      <c r="V17" s="3">
-        <v>1664100</v>
       </c>
       <c r="W17" s="3">
         <v>1664100</v>
       </c>
       <c r="X17" s="3">
+        <v>1664100</v>
+      </c>
+      <c r="Y17" s="3">
         <v>1623200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1640000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1643600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1636200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1966600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2194200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2270600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2304900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2192700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2099500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1970400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2046900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1864000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1879800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1793500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1928300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1964600</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1946400</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1779000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1930,86 +1960,89 @@
       <c r="P18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3">
         <v>202700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>186200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>153000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>278800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>236800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>245300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>268200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>255200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>208800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>189500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>68700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>250300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>217200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>277100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>293400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>313000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>333100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>273000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>304000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>272800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>217100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>211500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>249200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>260500</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>180000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>248700</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,8 +2085,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2096,86 +2130,89 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>-36800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-30000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-46800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-6400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-24300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-14000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-19300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-19900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-9100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-45500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-17900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-26500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-27500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-21900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-30500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-26600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-14800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-20800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-25100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-29400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-27800</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-19300</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-23800</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-16100</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2218,86 +2255,89 @@
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>268600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>250400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>193000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>353600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>293400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>293100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>351600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>311200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>282700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>249600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>149300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>300500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>304900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>353000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>368300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>389300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>389100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>306800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>349000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>311100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>259100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>240600</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>283300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>307300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>226900</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>298900</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2340,8 +2380,8 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2358,8 +2398,8 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>8</v>
@@ -2376,21 +2416,21 @@
       <c r="AB22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD22" s="3">
         <v>3500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>3000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>4600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>3500</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2400,8 +2440,8 @@
       <c r="AJ22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK22" s="3">
-        <v>0</v>
+      <c r="AK22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL22" s="3">
         <v>0</v>
@@ -2418,8 +2458,11 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2462,86 +2505,89 @@
       <c r="P23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="3">
         <v>165800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>156200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>106100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>272400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>212500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>231300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>261000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>235900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>202500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>169500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>59600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>204900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>195800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>247500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>261200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>287600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>302600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>246400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>289200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>252000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>192000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>182100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>221400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>241200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>156200</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>232600</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2584,86 +2630,89 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3">
         <v>69400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>38000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>49400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>77800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>51100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>58600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>61600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>61100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>51100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>48000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>25600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>60600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>72900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>83900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>78800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>77800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>52000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>79200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>78900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>66300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>63700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>63100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>90100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>74200</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>46100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>74900</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,8 +2833,11 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2828,86 +2880,89 @@
       <c r="P26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="3">
         <v>96400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>118100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>56700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>194600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>161500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>172700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>199400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>174800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>151400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>121500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>34000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>144300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>122900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>163600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>182400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>209700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>250600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>167200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>210400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>185700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>128300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>119000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>131300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>167000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>110100</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>157700</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2950,86 +3005,89 @@
       <c r="P27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="3">
         <v>87500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>106100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>47700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>187300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>155600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>166400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>194700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>168500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>144200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>116200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>35100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>138000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>117700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>156600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>174600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>202300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>242000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>160200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>201100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>178700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>119200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>112400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>123200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>159800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>100900</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>153400</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3194,8 +3255,8 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -3236,8 +3297,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -3254,12 +3315,12 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>83000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,8 +3583,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3560,86 +3630,89 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>36800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>30000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>46800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>6400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>24300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>14000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>19300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>6200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>19900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>9100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>45500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>17900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>26500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>27500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>21900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>30500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>26600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>14800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>20800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>25100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>29400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>27800</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>19300</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>23800</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3682,86 +3755,89 @@
       <c r="P33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R33" s="3">
         <v>87500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>106100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>47700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>187300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>155600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>166400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>194700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>168500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>144200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>116200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>35100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>138000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>117700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>156600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>174600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>202300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>242000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>160200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>201100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>178700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>202100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>112400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>123200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>159800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>100900</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>153400</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,8 +3958,11 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3926,213 +4005,219 @@
       <c r="P35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="3">
         <v>87500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>106100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>47700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>187300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>155600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>166400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>194700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>168500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>144200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>116200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>35100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>138000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>117700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>156600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>174600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>202300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>242000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>160200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>201100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>178700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>202100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>112400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>123200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>159800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>100900</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>153400</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1285700</v>
+      </c>
+      <c r="E41" s="3">
         <v>881300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>974700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>809600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1134700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1065300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>996700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>963900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>779200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1296300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1323600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1063400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>915600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>768100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1004500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1155700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>790200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>798200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1207400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1235800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1095500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1366900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1327200</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AC41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD41" s="3">
         <v>731100</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AG41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH41" s="3">
         <v>1192700</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AK41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL41" s="3">
         <v>765500</v>
       </c>
-      <c r="AL41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AO41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP41" s="3">
         <v>1128300</v>
       </c>
-      <c r="AP41" s="3" t="s">
+      <c r="AQ41" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4350,11 +4440,11 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>17600</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -4362,11 +4452,11 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>5600</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -4374,951 +4464,975 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>33700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>57300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>79100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>92900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>94900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>79700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>55100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>50700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>40000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>51600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>44100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>53700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>55400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1535200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1377200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1463100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>547000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1291300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1233400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1432900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>145300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>844700</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>650600</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>959800</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>162200</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>746800</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>756100</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>1235400</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>130200</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>1083700</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1869900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1769600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2191900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1741500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1776900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1669800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1961800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1718400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1771400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1745900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2153300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1703100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1828500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1806200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1655800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1736800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1695900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1556700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1276200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1317000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1403800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1398800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1160500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1289700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1269400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1642300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1592500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1825900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1801200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1841400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1588900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1507800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1574500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1567200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1444100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1454900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1523400</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1654800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1528200</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1502000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2703900</v>
+      </c>
+      <c r="E44" s="3">
         <v>2637500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2568800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2586400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2619800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2475100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2365700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2509800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2316900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2296300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2306300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2325700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2485500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2523300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2551800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2583500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2504400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2205100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1917900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1843200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1714000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1601800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1486100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1651300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1854200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2147200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2052400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2319200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2172200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2216700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2046200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1890500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1936600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1912400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1843000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1791800</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1767300</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1821300</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1750300</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1721800</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>799800</v>
+      </c>
+      <c r="E45" s="3">
         <v>760600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>39100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>674200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>644700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>618300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>172600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>601700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>612500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>682600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>46400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>607600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>597200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>562000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>549900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>612000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>564100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>554400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>471600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>503800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>451400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>429000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>400700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>450000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>474500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>510500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>516900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>547800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>496600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>456900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>449100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>574900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>565400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>414500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>394400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>378900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>381600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>404400</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>355700</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>375400</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6659300</v>
+      </c>
+      <c r="E46" s="3">
         <v>6048900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5916800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5811800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6176100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5828500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5583500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5793800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5480100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6021000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5957900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5757100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5905800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5752500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5856900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6167700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5609800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5165200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4913100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4951300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4708900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4850200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4430000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4926200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4975400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5763200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5439900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5984300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5703300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5947900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5422200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4818000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4727200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4853800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4609300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>4372300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>4428400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>5115900</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>4892600</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>4682800</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>163900</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>172500</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>156400</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3">
         <v>119900</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V47" s="3">
         <v>110800</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z47" s="3">
         <v>123400</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AC47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD47" s="3">
         <v>145600</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AG47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH47" s="3">
         <v>132600</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AK47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL47" s="3">
         <v>127800</v>
       </c>
-      <c r="AL47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AO47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP47" s="3">
         <v>152700</v>
       </c>
-      <c r="AP47" s="3" t="s">
+      <c r="AQ47" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3262600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3293600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3329100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3272900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3267400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3124500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3075200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3165900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3020900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2942100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2961300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2827100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2864800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2797000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2740700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2645900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2517000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2284100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2135900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2136800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2035500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2050200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1953200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2113700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2208500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2499200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2434400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2585400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2371900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2398700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1915600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1707900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1710600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1706900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1696600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1644700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1666900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1798500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1787500</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1753900</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1537000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1551300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1562400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1584800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1595500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1568400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1556000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1642900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1647700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1667200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1688100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1678500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1726300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1737600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1782000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1870800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1773500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1622500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1547500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1585900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1531300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1594900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1534200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1731200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1861900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2149700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2091700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2296700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2123400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2125800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2034300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1891500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1907000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1837500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1868600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1843900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1907300</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>2181300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>2221400</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>2151800</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>306300</v>
+      </c>
+      <c r="E52" s="3">
         <v>343100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>97900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>246400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>242400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>412600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>88700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>263400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>236900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>232900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>45100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>188000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>175800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>180800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>365400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>484000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>462600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>488300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>392800</v>
-      </c>
-      <c r="V52" s="3">
-        <v>573600</v>
       </c>
       <c r="W52" s="3">
         <v>573600</v>
       </c>
       <c r="X52" s="3">
+        <v>573600</v>
+      </c>
+      <c r="Y52" s="3">
         <v>582100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>513200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>690600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>656500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>724300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>588400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>858300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>759100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>714200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>501900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>568300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>573700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>567600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>438400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>586100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>587000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>632300</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>471000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>648700</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12237400</v>
+      </c>
+      <c r="E54" s="3">
         <v>11701500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11546000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>11350200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11712600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11276300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10789700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11184300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10697200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11165700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11127200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10728700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10974300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10782900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10864900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11168400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10362900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>9560100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9100000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>9247600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>8849200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9077500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8554000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>9461700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>9702300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>11136300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>10700100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11724700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>10957700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>11186600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>10006600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>8985700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>8918400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>8965800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>8740700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>8447000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>8589600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>9728000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>9525100</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>9237100</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1201800</v>
+      </c>
+      <c r="E57" s="3">
         <v>1151000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1215900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1123600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1225000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1173900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1134200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1166400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1063600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1089100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1117300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1027300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1157100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1183800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1135600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1143400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1169700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1016400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>902500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>841800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>864000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>869000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>799000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>776200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>687700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1023300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>939800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1034000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>976700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1000700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>898900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>834100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>880500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>879600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>850200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>806000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>842500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>859100</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>806000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>735800</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>218100</v>
+      </c>
+      <c r="E58" s="3">
         <v>220200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>127200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>121100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>499800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>492400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>484400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>476600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>96300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>377300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>403700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>392000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>367500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>79300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>62200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>412100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>401800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>379900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>52900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>76100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>80300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>77900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>307900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>585200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>626300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>421700</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD58" s="3">
+      <c r="AD58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE58" s="3">
         <v>136500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>358100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>365400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>264800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>292400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>42600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>287700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>292600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>44100</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>71800</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>35400</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>183800</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>148300</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1619800</v>
+      </c>
+      <c r="E59" s="3">
         <v>1524500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>562700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1433900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1416100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1181200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>359000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1241100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1162300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1236100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>364000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1199400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1255200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1221200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1196100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1225000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1174400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1101300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1284700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1130300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1080400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1033300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>937500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1055600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1130200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1295300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1691200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1493800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1394200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1329400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1233900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1172500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1179300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1072800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1065900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1033600</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1044100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1077500</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>983000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1039800</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3039700</v>
+      </c>
+      <c r="E60" s="3">
         <v>2895700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2794400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2678500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3140900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2847500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2722800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2884100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2322200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2702500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2745800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2618700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2779800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2484300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2393900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2780500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2745900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2497700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2240100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2048300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2024600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1980200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2044500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2417000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2444300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2740300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2631000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2664200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2728900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2695500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2397600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2299100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2102400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2240000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2208700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1883700</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1958400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>1972100</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>1972800</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>1923900</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1904500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1408900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1537100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1537300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1530200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1434300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1391400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1470000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1779800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1756000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1779300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1731400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1780200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2064300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2078400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2066500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1586600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1474200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1413200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1727100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1689900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1736700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1234100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1560700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1625600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1812800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1751800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2219100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2045400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2067500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1704600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1552100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1759400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1689900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1699600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1906300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1951800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2568200</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>2501000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2405800</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>171400</v>
+      </c>
+      <c r="E62" s="3">
         <v>209400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>202900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>192700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>180500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>132700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>135900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>145700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>169300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>136500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>141400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>146500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>141300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>115800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1099100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>988700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1040600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1224000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1303100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1474700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1452900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1510700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1902000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1880400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1873600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2198700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2068800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2405800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2063200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2007000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1834800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1562400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1601400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1610000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1622200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1656800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1732900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1830300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1908800</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>2034200</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6060000</v>
+      </c>
+      <c r="E66" s="3">
         <v>5483700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5506400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5407100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5888200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5382500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5190400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5494500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5250000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5540700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5662600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5390100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5630900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5620400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5778700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6043600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5565900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5366100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5113500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5402700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5311300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5373700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5313200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6000100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6129700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6968300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6662400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7518400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>7048900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6979600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6157000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5610600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5666300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>5734300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>5722900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>5616700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>5817400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>6567200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>6569700</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>6541100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,44 +7938,47 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="3">
         <v>5845300</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="3">
         <v>4775900</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N72" s="3">
         <v>4855800</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>8</v>
       </c>
@@ -7814,8 +7988,8 @@
       <c r="Q72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
+      <c r="R72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S72" s="3">
         <v>0</v>
@@ -7889,8 +8063,11 @@
       <c r="AP72" s="3">
         <v>0</v>
       </c>
+      <c r="AQ72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5937900</v>
+      </c>
+      <c r="E76" s="3">
         <v>5982900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5810600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5710400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5590000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5668400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5389600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5476500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5206000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5395200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5244600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5126400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5120300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4950300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5086200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5124800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4797000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4194000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3986500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3844800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3538000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3703800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3240800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3461700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3572600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4168100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4037700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4206300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3908800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4207000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3849600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3375100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3252200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3231500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3017800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>2830400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>2772200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>3160700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>2955400</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>2696000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,135 +8688,141 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8670,86 +8865,89 @@
       <c r="P81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="3">
         <v>87500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>106100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>47700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>187300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>155600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>166400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>194700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>168500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>144200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>116200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>35100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>138000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>117700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>156600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>174600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>202300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>242000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>160200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>201100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>178700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>202100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>112400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>123200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>159800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>100900</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>153400</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>123200</v>
+      </c>
+      <c r="E83" s="3">
         <v>125300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>41500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>99400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>94500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>100300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>46900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>99000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>87200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>96400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>26800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>88000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>87600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>92100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>102700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>94300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>86900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>81200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>80800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>61800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>90600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>75300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>80200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>80000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>89800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>95600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>105600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>102400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>102500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>98200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>86600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>60400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>59800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>59000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>67100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>58400</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>61900</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>66100</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>70700</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>66300</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>212000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-46900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>299200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>195300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>296200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>97300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>296600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>352600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>203000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>166600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>391500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>315200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>339600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>265300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>328200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>122400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>125100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-25600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>112300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>238500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>127900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>12400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>270600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>295400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-38000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>306100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>244700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>372600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>313700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>172600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>311300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>212900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>290200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>84800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>262000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>156300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>205400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>72100</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>247400</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>264300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-73700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-81100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-87200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-102500</v>
       </c>
-      <c r="G91" s="3">
-        <v>-97900</v>
-      </c>
       <c r="H91" s="3">
+        <v>-97800</v>
+      </c>
+      <c r="I91" s="3">
         <v>-91300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-112000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-141100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-124800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-93200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-146000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-104200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-152300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-145000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1535000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1348000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1529000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1110000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1109000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1043000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-84200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-79000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-90900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-79200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-69800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-102200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>2700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>86400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-94700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-100600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-72300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-63400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-68600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-79000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-62000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-54300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-70700</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-122100</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-60600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-74600</v>
+      </c>
+      <c r="E94" s="3">
         <v>4300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-107500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-103700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>112600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-60100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-174100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-137400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-121900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-92500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-167300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-101700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-152300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-138500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-134800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-128500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-148200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-104500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-37300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-99000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-80400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-78800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-90800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-72100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-48400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-93100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-164800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-115900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-146300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-92400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>177600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-63300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-57900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-78600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-83000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>42600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-64800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-85300</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-87900</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
+      <c r="D96" s="3">
+        <v>188600</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3">
         <v>4000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>372100</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>36500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>323200</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O96" s="3">
         <v>12200</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q96" s="3">
         <v>307800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-4200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-302000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-3700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-277000</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-38400</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-140900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-100</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-317400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-265000</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-7300</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-3600</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-269500</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-1500</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-4400</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-5200</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-33500</v>
+        <v>271600</v>
       </c>
       <c r="E100" s="3">
         <v>-33500</v>
       </c>
       <c r="F100" s="3">
+        <v>-33500</v>
+      </c>
+      <c r="G100" s="3">
         <v>-417400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-392600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-31300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-19000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-58100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-607000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-31800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-29200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-45300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-16900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-342000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-346400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>368600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-26700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-321700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-77800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-31800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-292800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>77300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-215000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>182000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>357600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-418700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-583600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-38900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-28200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>21200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-522700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-49700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-62300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-680300</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-9200</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-18400</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-166600</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-39700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>9800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-7500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>9100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-23800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-11200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>7900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-7000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-15200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>4700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>22200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-15500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>5000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>22100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>19100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>14100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-6200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>27400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-6500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-10900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-19600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-21100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>15100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>4600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>12400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-6100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>4900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>8500</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-9700</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-13600</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-100</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>8400</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>420300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-62700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>147000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-335500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-33700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>113400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>149600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-528400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>51300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>171200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>157000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>178300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-222200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-168400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>367500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-27800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-449900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>16300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>121800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-251500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>38300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-33200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>212400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>84700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>551000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>40800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-146900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-411600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>53700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>462100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>186000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-292400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>30800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>142200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-445800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-2000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>152100</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>11800</v>
       </c>
     </row>
